--- a/e2e/expectedData/sub_Master_Benefit_Medical.xlsx
+++ b/e2e/expectedData/sub_Master_Benefit_Medical.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>DAFTAR PEMBAYARAN MEDICAL KARYAWAN</t>
   </si>
@@ -104,6 +104,9 @@
     <t>CLAUDIO DA COSTA ALVES</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
     <t>Lestari Putri Cantika</t>
   </si>
   <si>
@@ -116,7 +119,7 @@
     <t>$ 9.00</t>
   </si>
   <si>
-    <t>DILI, 26 AGUSTUS 2026</t>
+    <t>DILI, 09 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -821,7 +824,7 @@
         <v>13</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>15</v>
@@ -844,10 +847,10 @@
         <v>999999</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>23</v>
@@ -867,7 +870,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -877,7 +880,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -885,18 +888,18 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17"/>
       <c r="G17"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18"/>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:9" customHeight="1" ht="37.5">
@@ -906,20 +909,20 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20"/>
       <c r="G20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E21"/>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/sub_Master_Benefit_Medical.xlsx
+++ b/e2e/expectedData/sub_Master_Benefit_Medical.xlsx
@@ -59,24 +59,27 @@
     <t>VI</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>Medical</t>
+  </si>
+  <si>
+    <t>$ 1.00</t>
+  </si>
+  <si>
+    <t>Jan-26</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>Medical</t>
-  </si>
-  <si>
-    <t>$ 1.00</t>
-  </si>
-  <si>
-    <t>Jan-26</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
     <t>FRIESCA AMELIA</t>
   </si>
   <si>
@@ -104,9 +107,6 @@
     <t>CLAUDIO DA COSTA ALVES</t>
   </si>
   <si>
-    <t>Outsource</t>
-  </si>
-  <si>
     <t>Lestari Putri Cantika</t>
   </si>
   <si>
@@ -119,7 +119,7 @@
     <t>$ 9.00</t>
   </si>
   <si>
-    <t>DILI, 09 SEPTEMBER 2026</t>
+    <t>DILI, 10 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -650,7 +650,7 @@
         <v>19</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>15</v>
@@ -673,13 +673,13 @@
         <v>91009</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>15</v>
@@ -702,13 +702,13 @@
         <v>74003</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>15</v>
@@ -731,13 +731,13 @@
         <v>91015</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>15</v>
@@ -760,13 +760,13 @@
         <v>26013</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>15</v>
@@ -789,13 +789,13 @@
         <v>95008</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>15</v>
@@ -818,13 +818,13 @@
         <v>24005</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>15</v>
@@ -853,7 +853,7 @@
         <v>31</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>15</v>
